--- a/output/laminas_comunales/comunal_i_ingr_median_a_2024_nuble.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2024_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>5.351104431568743</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>7.489164539882776</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>5.231804878048774</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>2.31096911608093</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>7.134680134680127</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>5.619145299145289</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>10.8549101456304</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>7.259805362918548</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>9.550642152626709</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -603,9 +571,6 @@
       <c r="E11">
         <v>9.085924277813229</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,9 +590,6 @@
       <c r="E12">
         <v>7.396966035709496</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -647,9 +609,6 @@
       <c r="E13">
         <v>12.74727576205679</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -669,9 +628,6 @@
       <c r="E14">
         <v>5.950046166440459</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -691,9 +647,6 @@
       <c r="E15">
         <v>8.040375023822467</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -713,9 +666,6 @@
       <c r="E16">
         <v>6.164430779412378</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -735,9 +685,6 @@
       <c r="E17">
         <v>10.09084533459461</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -757,9 +704,6 @@
       <c r="E18">
         <v>8.329089683563806</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -779,9 +723,6 @@
       <c r="E19">
         <v>9.643906945494241</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -801,9 +742,6 @@
       <c r="E20">
         <v>9.116122092104394</v>
       </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -823,9 +761,6 @@
       <c r="E21">
         <v>5.589942294580341</v>
       </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -844,9 +779,6 @@
       </c>
       <c r="E22">
         <v>10.41773913043478</v>
-      </c>
-      <c r="F22" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2024_nuble.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2024_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,7 +385,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ránquil</t>
+          <t>Ranquil</t>
         </is>
       </c>
       <c r="B2">
@@ -518,266 +518,285 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Quillón</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B9">
-        <v>747810</v>
+        <v>764205</v>
       </c>
       <c r="C9">
-        <v>697195</v>
+        <v>715231</v>
       </c>
       <c r="D9">
-        <v>50615</v>
+        <v>48974</v>
       </c>
       <c r="E9">
-        <v>7.259805362918548</v>
+        <v>6.847298285449033</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>Quillón</t>
         </is>
       </c>
       <c r="B10">
-        <v>735282</v>
+        <v>747810</v>
       </c>
       <c r="C10">
-        <v>671180</v>
+        <v>697195</v>
       </c>
       <c r="D10">
-        <v>64102</v>
+        <v>50615</v>
       </c>
       <c r="E10">
-        <v>9.550642152626709</v>
+        <v>7.259805362918548</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>San Fabián</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="B11">
-        <v>724150</v>
+        <v>735282</v>
       </c>
       <c r="C11">
-        <v>663834.5</v>
+        <v>671180</v>
       </c>
       <c r="D11">
-        <v>60315.5</v>
+        <v>64102</v>
       </c>
       <c r="E11">
-        <v>9.085924277813229</v>
+        <v>9.550642152626709</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>San Fabián</t>
         </is>
       </c>
       <c r="B12">
-        <v>720000</v>
+        <v>724150</v>
       </c>
       <c r="C12">
-        <v>670410</v>
+        <v>663834.5</v>
       </c>
       <c r="D12">
-        <v>49590</v>
+        <v>60315.5</v>
       </c>
       <c r="E12">
-        <v>7.396966035709496</v>
+        <v>9.085924277813229</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>Bulnes</t>
         </is>
       </c>
       <c r="B13">
-        <v>710610</v>
+        <v>720000</v>
       </c>
       <c r="C13">
-        <v>630268</v>
+        <v>670410</v>
       </c>
       <c r="D13">
-        <v>80342</v>
+        <v>49590</v>
       </c>
       <c r="E13">
-        <v>12.74727576205679</v>
+        <v>7.396966035709496</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pemuco</t>
+          <t>Pinto</t>
         </is>
       </c>
       <c r="B14">
-        <v>698241</v>
+        <v>710610</v>
       </c>
       <c r="C14">
-        <v>659028.5</v>
+        <v>630268</v>
       </c>
       <c r="D14">
-        <v>39212.5</v>
+        <v>80342</v>
       </c>
       <c r="E14">
-        <v>5.950046166440459</v>
+        <v>12.74727576205679</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>Pemuco</t>
         </is>
       </c>
       <c r="B15">
-        <v>697291.5</v>
+        <v>698241</v>
       </c>
       <c r="C15">
-        <v>645399</v>
+        <v>659028.5</v>
       </c>
       <c r="D15">
-        <v>51892.5</v>
+        <v>39212.5</v>
       </c>
       <c r="E15">
-        <v>8.040375023822467</v>
+        <v>5.950046166440459</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
+          <t>Quirihue</t>
         </is>
       </c>
       <c r="B16">
-        <v>693000</v>
+        <v>697291.5</v>
       </c>
       <c r="C16">
-        <v>652761</v>
+        <v>645399</v>
       </c>
       <c r="D16">
-        <v>40239</v>
+        <v>51892.5</v>
       </c>
       <c r="E16">
-        <v>6.164430779412378</v>
+        <v>8.040375023822467</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Coihueco</t>
+          <t>San Nicolás</t>
         </is>
       </c>
       <c r="B17">
-        <v>675000</v>
+        <v>693000</v>
       </c>
       <c r="C17">
-        <v>613130</v>
+        <v>652761</v>
       </c>
       <c r="D17">
-        <v>61870</v>
+        <v>40239</v>
       </c>
       <c r="E17">
-        <v>10.09084533459461</v>
+        <v>6.164430779412378</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
+          <t>Coihueco</t>
         </is>
       </c>
       <c r="B18">
-        <v>657329</v>
+        <v>675000</v>
       </c>
       <c r="C18">
-        <v>606789</v>
+        <v>613130</v>
       </c>
       <c r="D18">
-        <v>50540</v>
+        <v>61870</v>
       </c>
       <c r="E18">
-        <v>8.329089683563806</v>
+        <v>10.09084533459461</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>El Carmen</t>
+          <t>Cobquecura</t>
         </is>
       </c>
       <c r="B19">
-        <v>652765</v>
+        <v>657329</v>
       </c>
       <c r="C19">
-        <v>595350</v>
+        <v>606789</v>
       </c>
       <c r="D19">
-        <v>57415</v>
+        <v>50540</v>
       </c>
       <c r="E19">
-        <v>9.643906945494241</v>
+        <v>8.329089683563806</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="B20">
-        <v>642084</v>
+        <v>652765</v>
       </c>
       <c r="C20">
-        <v>588441</v>
+        <v>595350</v>
       </c>
       <c r="D20">
-        <v>53643</v>
+        <v>57415</v>
       </c>
       <c r="E20">
-        <v>9.116122092104394</v>
+        <v>9.643906945494241</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
+          <t>San Ignacio</t>
         </is>
       </c>
       <c r="B21">
-        <v>634944</v>
+        <v>642084</v>
       </c>
       <c r="C21">
-        <v>601330</v>
+        <v>588441</v>
       </c>
       <c r="D21">
-        <v>33614</v>
+        <v>53643</v>
       </c>
       <c r="E21">
-        <v>5.589942294580341</v>
+        <v>9.116122092104394</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>634944</v>
+      </c>
+      <c r="C22">
+        <v>601330</v>
+      </c>
+      <c r="D22">
+        <v>33614</v>
+      </c>
+      <c r="E22">
+        <v>5.589942294580341</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Ninhue</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>634902</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>575000</v>
       </c>
-      <c r="D22">
+      <c r="D23">
         <v>59902</v>
       </c>
-      <c r="E22">
+      <c r="E23">
         <v>10.41773913043478</v>
       </c>
     </row>
@@ -946,7 +965,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ránquil</t>
+          <t>Ranquil</t>
         </is>
       </c>
       <c r="B16">

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2024_nuble.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2024_nuble.xlsx
@@ -807,7 +807,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -816,11 +816,6 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -828,9 +823,6 @@
           <t>Bulnes</t>
         </is>
       </c>
-      <c r="B2">
-        <v>720000</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -838,9 +830,6 @@
           <t>Chillán Viejo</t>
         </is>
       </c>
-      <c r="B3">
-        <v>772340</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -848,188 +837,131 @@
           <t>Chillán</t>
         </is>
       </c>
-      <c r="B4">
-        <v>844451</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>657329</v>
+          <t>Yungay</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coelemu</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>808969.5</v>
+          <t>Quillón</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Coihueco</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>675000</v>
+          <t>San Carlos</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>El Carmen</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>652765</v>
+          <t>Treguaco</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ninhue</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>634902</v>
+          <t>Ranquil</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ñiquén</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>768020</v>
+          <t>Portezuelo</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pemuco</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>698241</v>
+          <t>Cobquecura</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pinto</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>710610</v>
+          <t>Quirihue</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>634944</v>
+          <t>Coelemu</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Quillón</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>747810</v>
+          <t>Ninhue</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Quirihue</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>697291.5</v>
+          <t>Pinto</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ranquil</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>852400</v>
+          <t>San Ignacio</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>San Carlos</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>735282</v>
+          <t>Pemuco</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>San Fabián</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>724150</v>
+          <t>San Nicolás</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>642084</v>
+          <t>San Fabián</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>693000</v>
+          <t>Ñiquén</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Treguaco</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>795475</v>
+          <t>El Carmen</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Yungay</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>806988</v>
+          <t>Coihueco</t>
+        </is>
       </c>
     </row>
   </sheetData>
